--- a/data/delo_registers/11.2_Сводная_ведомость_поставщиков.xlsx
+++ b/data/delo_registers/11.2_Сводная_ведомость_поставщиков.xlsx
@@ -1754,7 +1754,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15.05.2026 17:29</t>
+          <t>15.05.2026 18:45</t>
         </is>
       </c>
     </row>
